--- a/EXCEL/Lego.xlsx
+++ b/EXCEL/Lego.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3502" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="87">
   <si>
     <t>Columna1</t>
   </si>
@@ -279,16 +279,13 @@
   <si>
     <t>Estatua</t>
   </si>
-  <si>
-    <t>Total</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,15 +307,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -452,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,10 +468,10 @@
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -489,9 +479,6 @@
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -512,15 +499,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -550,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I1571" displayName="Tabla2" name="Tabla2" id="1" totalsRowCount="1">
-  <autoFilter ref="A1:I1570"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I1517" displayName="Tabla2" name="Tabla2" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:I1517"/>
   <tableColumns count="9">
     <tableColumn name="Columna1" id="1" totalsRowLabel="Total"/>
     <tableColumn name="Code" id="2"/>
@@ -855,19 +833,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J1571"/>
+  <dimension ref="A1:J1517"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="24" width="7.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="25" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="26" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="26" width="11.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="26" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="24" width="12.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="24" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="24" width="25.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="26" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="20" width="7.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="21" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="22" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="22" width="11.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="22" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="20" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="20" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="20" width="25.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="22" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="23" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -5732,7 +5710,7 @@
       <c r="I174" s="7"/>
       <c r="J174" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="23.25">
       <c r="A175" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5760,7 +5738,7 @@
       <c r="I175" s="7"/>
       <c r="J175" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="23.25">
       <c r="A176" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5788,7 +5766,7 @@
       <c r="I176" s="7"/>
       <c r="J176" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="23.25">
       <c r="A177" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5816,7 +5794,7 @@
       <c r="I177" s="7"/>
       <c r="J177" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="23.25">
       <c r="A178" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5844,7 +5822,7 @@
       <c r="I178" s="7"/>
       <c r="J178" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="23.25">
       <c r="A179" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5872,7 +5850,7 @@
       <c r="I179" s="7"/>
       <c r="J179" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="23.25">
       <c r="A180" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5900,7 +5878,7 @@
       <c r="I180" s="7"/>
       <c r="J180" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="23.25">
       <c r="A181" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5928,7 +5906,7 @@
       <c r="I181" s="7"/>
       <c r="J181" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="23.25">
       <c r="A182" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5956,7 +5934,7 @@
       <c r="I182" s="7"/>
       <c r="J182" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="23.25">
       <c r="A183" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -5984,7 +5962,7 @@
       <c r="I183" s="7"/>
       <c r="J183" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="23.25">
       <c r="A184" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6012,7 +5990,7 @@
       <c r="I184" s="7"/>
       <c r="J184" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="23.25">
       <c r="A185" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6040,7 +6018,7 @@
       <c r="I185" s="7"/>
       <c r="J185" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="23.25">
       <c r="A186" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6068,7 +6046,7 @@
       <c r="I186" s="7"/>
       <c r="J186" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="23.25">
       <c r="A187" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6096,7 +6074,7 @@
       <c r="I187" s="7"/>
       <c r="J187" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="23.25">
       <c r="A188" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6122,7 +6100,7 @@
       <c r="I188" s="7"/>
       <c r="J188" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="23.25">
       <c r="A189" s="9"/>
       <c r="B189" s="7">
         <v>395726</v>
@@ -6148,7 +6126,7 @@
       <c r="I189" s="7"/>
       <c r="J189" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="23.25">
       <c r="A190" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6176,7 +6154,7 @@
       <c r="I190" s="7"/>
       <c r="J190" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="23.25">
       <c r="A191" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6200,7 +6178,7 @@
       <c r="I191" s="7"/>
       <c r="J191" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="23.25">
       <c r="A192" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6224,7 +6202,7 @@
       <c r="I192" s="7"/>
       <c r="J192" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="23.25">
       <c r="A193" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6252,7 +6230,7 @@
       <c r="I193" s="7"/>
       <c r="J193" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="23.25">
       <c r="A194" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6280,7 +6258,7 @@
       <c r="I194" s="7"/>
       <c r="J194" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="23.25">
       <c r="A195" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -6308,7 +6286,7 @@
       <c r="I195" s="7"/>
       <c r="J195" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="23.25">
       <c r="A196" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
@@ -10994,7 +10972,7 @@
       <c r="E364" s="7">
         <v>4013</v>
       </c>
-      <c r="F364" s="13" t="s">
+      <c r="F364" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G364" s="8" t="s">
@@ -21166,7 +21144,7 @@
       <c r="A732" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B732" s="14">
+      <c r="B732" s="13">
         <v>4211054</v>
       </c>
       <c r="C732" s="7">
@@ -25451,12 +25429,12 @@
       <c r="D890" s="7">
         <v>1</v>
       </c>
-      <c r="E890" s="15"/>
-      <c r="F890" s="16" t="s">
+      <c r="E890" s="14"/>
+      <c r="F890" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G890" s="16"/>
-      <c r="H890" s="17" t="s">
+      <c r="G890" s="15"/>
+      <c r="H890" s="16" t="s">
         <v>53</v>
       </c>
       <c r="I890" s="7"/>
@@ -25475,12 +25453,12 @@
       <c r="D891" s="7">
         <v>1</v>
       </c>
-      <c r="E891" s="15"/>
-      <c r="F891" s="16" t="s">
+      <c r="E891" s="14"/>
+      <c r="F891" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G891" s="16"/>
-      <c r="H891" s="17" t="s">
+      <c r="G891" s="15"/>
+      <c r="H891" s="16" t="s">
         <v>53</v>
       </c>
       <c r="I891" s="7"/>
@@ -25490,23 +25468,23 @@
       <c r="A892" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B892" s="15">
+      <c r="B892" s="14">
         <v>6411327</v>
       </c>
-      <c r="C892" s="15">
+      <c r="C892" s="14">
         <v>8962</v>
       </c>
-      <c r="D892" s="15">
-        <v>1</v>
-      </c>
-      <c r="E892" s="15">
+      <c r="D892" s="14">
+        <v>1</v>
+      </c>
+      <c r="E892" s="14">
         <v>4526</v>
       </c>
-      <c r="F892" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G892" s="16"/>
-      <c r="H892" s="17" t="s">
+      <c r="F892" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G892" s="15"/>
+      <c r="H892" s="16" t="s">
         <v>53</v>
       </c>
       <c r="I892" s="7"/>
@@ -25516,23 +25494,23 @@
       <c r="A893" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B893" s="15">
+      <c r="B893" s="14">
         <v>4164021</v>
       </c>
-      <c r="C893" s="15">
+      <c r="C893" s="14">
         <v>8963</v>
       </c>
-      <c r="D893" s="15">
-        <v>1</v>
-      </c>
-      <c r="E893" s="15">
+      <c r="D893" s="14">
+        <v>1</v>
+      </c>
+      <c r="E893" s="14">
         <v>3999</v>
       </c>
-      <c r="F893" s="16"/>
-      <c r="G893" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="H893" s="17" t="s">
+      <c r="F893" s="15"/>
+      <c r="G893" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H893" s="16" t="s">
         <v>53</v>
       </c>
       <c r="I893" s="7"/>
@@ -28472,7 +28450,7 @@
       <c r="A1007" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1007" s="18">
+      <c r="B1007" s="17">
         <v>4210934</v>
       </c>
       <c r="C1007" s="7">
@@ -28606,7 +28584,7 @@
       <c r="A1012" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1012" s="18">
+      <c r="B1012" s="17">
         <v>4264569</v>
       </c>
       <c r="C1012" s="7">
@@ -28632,7 +28610,7 @@
       <c r="A1013" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1013" s="18">
+      <c r="B1013" s="17">
         <v>4502089</v>
       </c>
       <c r="C1013" s="7">
@@ -28660,7 +28638,7 @@
       <c r="A1014" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1014" s="18">
+      <c r="B1014" s="17">
         <v>4502089</v>
       </c>
       <c r="C1014" s="7">
@@ -28686,7 +28664,7 @@
       <c r="A1015" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1015" s="18">
+      <c r="B1015" s="17">
         <v>4508313</v>
       </c>
       <c r="C1015" s="7">
@@ -28712,7 +28690,7 @@
       <c r="A1016" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1016" s="18">
+      <c r="B1016" s="17">
         <v>4509911</v>
       </c>
       <c r="C1016" s="7">
@@ -28734,7 +28712,7 @@
       <c r="A1017" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1017" s="18">
+      <c r="B1017" s="17">
         <v>4515359</v>
       </c>
       <c r="C1017" s="7">
@@ -28858,7 +28836,7 @@
       <c r="A1022" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1022" s="18">
+      <c r="B1022" s="17">
         <v>6190437</v>
       </c>
       <c r="C1022" s="7">
@@ -31832,7 +31810,7 @@
       <c r="A1133" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1133" s="19">
+      <c r="B1133" s="18">
         <v>6289522</v>
       </c>
       <c r="C1133" s="7">
@@ -36378,7 +36356,7 @@
       <c r="A1334" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1334" s="15">
+      <c r="B1334" s="14">
         <v>6167483</v>
       </c>
       <c r="C1334" s="10"/>
@@ -39772,7 +39750,7 @@
       <c r="A1492" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1492" s="20">
+      <c r="B1492" s="19">
         <v>4211096</v>
       </c>
       <c r="C1492" s="7">
@@ -39800,7 +39778,7 @@
       <c r="A1493" s="6">
         <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
       </c>
-      <c r="B1493" s="20">
+      <c r="B1493" s="19">
         <v>4211096</v>
       </c>
       <c r="C1493" s="10"/>
@@ -40307,762 +40285,6 @@
       <c r="H1517" s="9"/>
       <c r="I1517" s="7"/>
       <c r="J1517" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1518" customHeight="1" ht="18.75">
-      <c r="A1518" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1518" s="21"/>
-      <c r="C1518" s="10"/>
-      <c r="D1518" s="10"/>
-      <c r="E1518" s="10"/>
-      <c r="F1518" s="9"/>
-      <c r="G1518" s="9"/>
-      <c r="H1518" s="9"/>
-      <c r="I1518" s="7"/>
-      <c r="J1518" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1519" customHeight="1" ht="18.75">
-      <c r="A1519" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1519" s="21"/>
-      <c r="C1519" s="10"/>
-      <c r="D1519" s="10"/>
-      <c r="E1519" s="10"/>
-      <c r="F1519" s="9"/>
-      <c r="G1519" s="9"/>
-      <c r="H1519" s="9"/>
-      <c r="I1519" s="7"/>
-      <c r="J1519" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1520" customHeight="1" ht="18.75">
-      <c r="A1520" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1520" s="21"/>
-      <c r="C1520" s="10"/>
-      <c r="D1520" s="10"/>
-      <c r="E1520" s="10"/>
-      <c r="F1520" s="9"/>
-      <c r="G1520" s="9"/>
-      <c r="H1520" s="9"/>
-      <c r="I1520" s="7"/>
-      <c r="J1520" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1521" customHeight="1" ht="18.75">
-      <c r="A1521" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1521" s="21"/>
-      <c r="C1521" s="10"/>
-      <c r="D1521" s="10"/>
-      <c r="E1521" s="10"/>
-      <c r="F1521" s="9"/>
-      <c r="G1521" s="9"/>
-      <c r="H1521" s="9"/>
-      <c r="I1521" s="7"/>
-      <c r="J1521" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1522" customHeight="1" ht="18.75">
-      <c r="A1522" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1522" s="21"/>
-      <c r="C1522" s="10"/>
-      <c r="D1522" s="10"/>
-      <c r="E1522" s="10"/>
-      <c r="F1522" s="9"/>
-      <c r="G1522" s="9"/>
-      <c r="H1522" s="9"/>
-      <c r="I1522" s="7"/>
-      <c r="J1522" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1523" customHeight="1" ht="18.75">
-      <c r="A1523" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1523" s="21"/>
-      <c r="C1523" s="10"/>
-      <c r="D1523" s="10"/>
-      <c r="E1523" s="10"/>
-      <c r="F1523" s="9"/>
-      <c r="G1523" s="9"/>
-      <c r="H1523" s="9"/>
-      <c r="I1523" s="7"/>
-      <c r="J1523" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1524" customHeight="1" ht="18.75">
-      <c r="A1524" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1524" s="21"/>
-      <c r="C1524" s="10"/>
-      <c r="D1524" s="10"/>
-      <c r="E1524" s="10"/>
-      <c r="F1524" s="9"/>
-      <c r="G1524" s="9"/>
-      <c r="H1524" s="9"/>
-      <c r="I1524" s="7"/>
-      <c r="J1524" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1525" customHeight="1" ht="18.75">
-      <c r="A1525" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1525" s="21"/>
-      <c r="C1525" s="10"/>
-      <c r="D1525" s="10"/>
-      <c r="E1525" s="10"/>
-      <c r="F1525" s="9"/>
-      <c r="G1525" s="9"/>
-      <c r="H1525" s="9"/>
-      <c r="I1525" s="7"/>
-      <c r="J1525" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1526" customHeight="1" ht="18.75">
-      <c r="A1526" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1526" s="21"/>
-      <c r="C1526" s="10"/>
-      <c r="D1526" s="10"/>
-      <c r="E1526" s="10"/>
-      <c r="F1526" s="9"/>
-      <c r="G1526" s="9"/>
-      <c r="H1526" s="9"/>
-      <c r="I1526" s="7"/>
-      <c r="J1526" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1527" customHeight="1" ht="18.75">
-      <c r="A1527" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1527" s="21"/>
-      <c r="C1527" s="10"/>
-      <c r="D1527" s="10"/>
-      <c r="E1527" s="10"/>
-      <c r="F1527" s="9"/>
-      <c r="G1527" s="9"/>
-      <c r="H1527" s="9"/>
-      <c r="I1527" s="7"/>
-      <c r="J1527" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1528" customHeight="1" ht="18.75">
-      <c r="A1528" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1528" s="21"/>
-      <c r="C1528" s="10"/>
-      <c r="D1528" s="10"/>
-      <c r="E1528" s="10"/>
-      <c r="F1528" s="9"/>
-      <c r="G1528" s="9"/>
-      <c r="H1528" s="9"/>
-      <c r="I1528" s="7"/>
-      <c r="J1528" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1529" customHeight="1" ht="18.75">
-      <c r="A1529" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1529" s="21"/>
-      <c r="C1529" s="10"/>
-      <c r="D1529" s="10"/>
-      <c r="E1529" s="10"/>
-      <c r="F1529" s="9"/>
-      <c r="G1529" s="9"/>
-      <c r="H1529" s="9"/>
-      <c r="I1529" s="7"/>
-      <c r="J1529" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1530" customHeight="1" ht="18.75">
-      <c r="A1530" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1530" s="21"/>
-      <c r="C1530" s="10"/>
-      <c r="D1530" s="10"/>
-      <c r="E1530" s="10"/>
-      <c r="F1530" s="9"/>
-      <c r="G1530" s="9"/>
-      <c r="H1530" s="9"/>
-      <c r="I1530" s="7"/>
-      <c r="J1530" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1531" customHeight="1" ht="18.75">
-      <c r="A1531" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1531" s="21"/>
-      <c r="C1531" s="10"/>
-      <c r="D1531" s="10"/>
-      <c r="E1531" s="10"/>
-      <c r="F1531" s="9"/>
-      <c r="G1531" s="9"/>
-      <c r="H1531" s="9"/>
-      <c r="I1531" s="7"/>
-      <c r="J1531" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1532" customHeight="1" ht="18.75">
-      <c r="A1532" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1532" s="21"/>
-      <c r="C1532" s="10"/>
-      <c r="D1532" s="10"/>
-      <c r="E1532" s="10"/>
-      <c r="F1532" s="9"/>
-      <c r="G1532" s="9"/>
-      <c r="H1532" s="9"/>
-      <c r="I1532" s="7"/>
-      <c r="J1532" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1533" customHeight="1" ht="18.75">
-      <c r="A1533" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1533" s="21"/>
-      <c r="C1533" s="10"/>
-      <c r="D1533" s="10"/>
-      <c r="E1533" s="10"/>
-      <c r="F1533" s="9"/>
-      <c r="G1533" s="9"/>
-      <c r="H1533" s="9"/>
-      <c r="I1533" s="7"/>
-      <c r="J1533" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1534" customHeight="1" ht="18.75">
-      <c r="A1534" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1534" s="21"/>
-      <c r="C1534" s="10"/>
-      <c r="D1534" s="10"/>
-      <c r="E1534" s="10"/>
-      <c r="F1534" s="9"/>
-      <c r="G1534" s="9"/>
-      <c r="H1534" s="9"/>
-      <c r="I1534" s="7"/>
-      <c r="J1534" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1535" customHeight="1" ht="18.75">
-      <c r="A1535" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1535" s="21"/>
-      <c r="C1535" s="10"/>
-      <c r="D1535" s="10"/>
-      <c r="E1535" s="10"/>
-      <c r="F1535" s="9"/>
-      <c r="G1535" s="9"/>
-      <c r="H1535" s="9"/>
-      <c r="I1535" s="7"/>
-      <c r="J1535" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1536" customHeight="1" ht="18.75">
-      <c r="A1536" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1536" s="21"/>
-      <c r="C1536" s="10"/>
-      <c r="D1536" s="10"/>
-      <c r="E1536" s="10"/>
-      <c r="F1536" s="9"/>
-      <c r="G1536" s="9"/>
-      <c r="H1536" s="9"/>
-      <c r="I1536" s="7"/>
-      <c r="J1536" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1537" customHeight="1" ht="18.75">
-      <c r="A1537" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1537" s="21"/>
-      <c r="C1537" s="10"/>
-      <c r="D1537" s="10"/>
-      <c r="E1537" s="10"/>
-      <c r="F1537" s="9"/>
-      <c r="G1537" s="9"/>
-      <c r="H1537" s="9"/>
-      <c r="I1537" s="7"/>
-      <c r="J1537" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1538" customHeight="1" ht="18.75">
-      <c r="A1538" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1538" s="21"/>
-      <c r="C1538" s="10"/>
-      <c r="D1538" s="10"/>
-      <c r="E1538" s="10"/>
-      <c r="F1538" s="9"/>
-      <c r="G1538" s="9"/>
-      <c r="H1538" s="9"/>
-      <c r="I1538" s="7"/>
-      <c r="J1538" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1539" customHeight="1" ht="18.75">
-      <c r="A1539" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1539" s="21"/>
-      <c r="C1539" s="10"/>
-      <c r="D1539" s="10"/>
-      <c r="E1539" s="10"/>
-      <c r="F1539" s="9"/>
-      <c r="G1539" s="9"/>
-      <c r="H1539" s="9"/>
-      <c r="I1539" s="7"/>
-      <c r="J1539" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1540" customHeight="1" ht="18.75">
-      <c r="A1540" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1540" s="21"/>
-      <c r="C1540" s="10"/>
-      <c r="D1540" s="10"/>
-      <c r="E1540" s="10"/>
-      <c r="F1540" s="9"/>
-      <c r="G1540" s="9"/>
-      <c r="H1540" s="9"/>
-      <c r="I1540" s="7"/>
-      <c r="J1540" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1541" customHeight="1" ht="18.75">
-      <c r="A1541" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1541" s="21"/>
-      <c r="C1541" s="10"/>
-      <c r="D1541" s="10"/>
-      <c r="E1541" s="10"/>
-      <c r="F1541" s="9"/>
-      <c r="G1541" s="9"/>
-      <c r="H1541" s="9"/>
-      <c r="I1541" s="7"/>
-      <c r="J1541" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1542" customHeight="1" ht="18.75">
-      <c r="A1542" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1542" s="21"/>
-      <c r="C1542" s="10"/>
-      <c r="D1542" s="10"/>
-      <c r="E1542" s="10"/>
-      <c r="F1542" s="9"/>
-      <c r="G1542" s="9"/>
-      <c r="H1542" s="9"/>
-      <c r="I1542" s="7"/>
-      <c r="J1542" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1543" customHeight="1" ht="18.75">
-      <c r="A1543" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1543" s="21"/>
-      <c r="C1543" s="10"/>
-      <c r="D1543" s="10"/>
-      <c r="E1543" s="10"/>
-      <c r="F1543" s="9"/>
-      <c r="G1543" s="9"/>
-      <c r="H1543" s="9"/>
-      <c r="I1543" s="7"/>
-      <c r="J1543" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1544" customHeight="1" ht="18.75">
-      <c r="A1544" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1544" s="21"/>
-      <c r="C1544" s="10"/>
-      <c r="D1544" s="10"/>
-      <c r="E1544" s="10"/>
-      <c r="F1544" s="9"/>
-      <c r="G1544" s="9"/>
-      <c r="H1544" s="9"/>
-      <c r="I1544" s="7"/>
-      <c r="J1544" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1545" customHeight="1" ht="18.75">
-      <c r="A1545" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1545" s="21"/>
-      <c r="C1545" s="10"/>
-      <c r="D1545" s="10"/>
-      <c r="E1545" s="10"/>
-      <c r="F1545" s="9"/>
-      <c r="G1545" s="9"/>
-      <c r="H1545" s="9"/>
-      <c r="I1545" s="7"/>
-      <c r="J1545" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1546" customHeight="1" ht="18.75">
-      <c r="A1546" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1546" s="21"/>
-      <c r="C1546" s="10"/>
-      <c r="D1546" s="10"/>
-      <c r="E1546" s="10"/>
-      <c r="F1546" s="9"/>
-      <c r="G1546" s="9"/>
-      <c r="H1546" s="9"/>
-      <c r="I1546" s="7"/>
-      <c r="J1546" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1547" customHeight="1" ht="18.75">
-      <c r="A1547" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1547" s="21"/>
-      <c r="C1547" s="10"/>
-      <c r="D1547" s="10"/>
-      <c r="E1547" s="10"/>
-      <c r="F1547" s="9"/>
-      <c r="G1547" s="9"/>
-      <c r="H1547" s="9"/>
-      <c r="I1547" s="7"/>
-      <c r="J1547" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1548" customHeight="1" ht="18.75">
-      <c r="A1548" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1548" s="21"/>
-      <c r="C1548" s="10"/>
-      <c r="D1548" s="10"/>
-      <c r="E1548" s="10"/>
-      <c r="F1548" s="9"/>
-      <c r="G1548" s="9"/>
-      <c r="H1548" s="9"/>
-      <c r="I1548" s="7"/>
-      <c r="J1548" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1549" customHeight="1" ht="18.75">
-      <c r="A1549" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1549" s="21"/>
-      <c r="C1549" s="10"/>
-      <c r="D1549" s="10"/>
-      <c r="E1549" s="10"/>
-      <c r="F1549" s="9"/>
-      <c r="G1549" s="9"/>
-      <c r="H1549" s="9"/>
-      <c r="I1549" s="7"/>
-      <c r="J1549" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1550" customHeight="1" ht="18.75">
-      <c r="A1550" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1550" s="21"/>
-      <c r="C1550" s="10"/>
-      <c r="D1550" s="10"/>
-      <c r="E1550" s="10"/>
-      <c r="F1550" s="9"/>
-      <c r="G1550" s="9"/>
-      <c r="H1550" s="9"/>
-      <c r="I1550" s="7"/>
-      <c r="J1550" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1551" customHeight="1" ht="18.75">
-      <c r="A1551" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1551" s="21"/>
-      <c r="C1551" s="10"/>
-      <c r="D1551" s="10"/>
-      <c r="E1551" s="10"/>
-      <c r="F1551" s="9"/>
-      <c r="G1551" s="9"/>
-      <c r="H1551" s="9"/>
-      <c r="I1551" s="7"/>
-      <c r="J1551" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1552" customHeight="1" ht="18.75">
-      <c r="A1552" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1552" s="21"/>
-      <c r="C1552" s="10"/>
-      <c r="D1552" s="10"/>
-      <c r="E1552" s="10"/>
-      <c r="F1552" s="9"/>
-      <c r="G1552" s="9"/>
-      <c r="H1552" s="9"/>
-      <c r="I1552" s="7"/>
-      <c r="J1552" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1553" customHeight="1" ht="18.75">
-      <c r="A1553" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1553" s="21"/>
-      <c r="C1553" s="10"/>
-      <c r="D1553" s="10"/>
-      <c r="E1553" s="10"/>
-      <c r="F1553" s="9"/>
-      <c r="G1553" s="9"/>
-      <c r="H1553" s="9"/>
-      <c r="I1553" s="7"/>
-      <c r="J1553" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1554" customHeight="1" ht="18.75">
-      <c r="A1554" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1554" s="21"/>
-      <c r="C1554" s="10"/>
-      <c r="D1554" s="10"/>
-      <c r="E1554" s="10"/>
-      <c r="F1554" s="9"/>
-      <c r="G1554" s="9"/>
-      <c r="H1554" s="9"/>
-      <c r="I1554" s="7"/>
-      <c r="J1554" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1555" customHeight="1" ht="18.75">
-      <c r="A1555" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1555" s="21"/>
-      <c r="C1555" s="10"/>
-      <c r="D1555" s="10"/>
-      <c r="E1555" s="10"/>
-      <c r="F1555" s="9"/>
-      <c r="G1555" s="9"/>
-      <c r="H1555" s="9"/>
-      <c r="I1555" s="7"/>
-      <c r="J1555" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1556" customHeight="1" ht="18.75">
-      <c r="A1556" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1556" s="21"/>
-      <c r="C1556" s="10"/>
-      <c r="D1556" s="10"/>
-      <c r="E1556" s="10"/>
-      <c r="F1556" s="9"/>
-      <c r="G1556" s="9"/>
-      <c r="H1556" s="9"/>
-      <c r="I1556" s="7"/>
-      <c r="J1556" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1557" customHeight="1" ht="18.75">
-      <c r="A1557" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1557" s="21"/>
-      <c r="C1557" s="10"/>
-      <c r="D1557" s="10"/>
-      <c r="E1557" s="10"/>
-      <c r="F1557" s="9"/>
-      <c r="G1557" s="9"/>
-      <c r="H1557" s="9"/>
-      <c r="I1557" s="7"/>
-      <c r="J1557" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1558" customHeight="1" ht="18.75">
-      <c r="A1558" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1558" s="21"/>
-      <c r="C1558" s="10"/>
-      <c r="D1558" s="10"/>
-      <c r="E1558" s="10"/>
-      <c r="F1558" s="9"/>
-      <c r="G1558" s="9"/>
-      <c r="H1558" s="9"/>
-      <c r="I1558" s="7"/>
-      <c r="J1558" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1559" customHeight="1" ht="18.75">
-      <c r="A1559" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1559" s="21"/>
-      <c r="C1559" s="10"/>
-      <c r="D1559" s="10"/>
-      <c r="E1559" s="10"/>
-      <c r="F1559" s="9"/>
-      <c r="G1559" s="9"/>
-      <c r="H1559" s="9"/>
-      <c r="I1559" s="7"/>
-      <c r="J1559" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1560" customHeight="1" ht="18.75">
-      <c r="A1560" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1560" s="21"/>
-      <c r="C1560" s="10"/>
-      <c r="D1560" s="10"/>
-      <c r="E1560" s="10"/>
-      <c r="F1560" s="9"/>
-      <c r="G1560" s="9"/>
-      <c r="H1560" s="9"/>
-      <c r="I1560" s="7"/>
-      <c r="J1560" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1561" customHeight="1" ht="18.75">
-      <c r="A1561" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1561" s="21"/>
-      <c r="C1561" s="10"/>
-      <c r="D1561" s="10"/>
-      <c r="E1561" s="10"/>
-      <c r="F1561" s="9"/>
-      <c r="G1561" s="9"/>
-      <c r="H1561" s="9"/>
-      <c r="I1561" s="7"/>
-      <c r="J1561" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1562" customHeight="1" ht="18.75">
-      <c r="A1562" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1562" s="21"/>
-      <c r="C1562" s="10"/>
-      <c r="D1562" s="10"/>
-      <c r="E1562" s="10"/>
-      <c r="F1562" s="9"/>
-      <c r="G1562" s="9"/>
-      <c r="H1562" s="9"/>
-      <c r="I1562" s="7"/>
-      <c r="J1562" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1563" customHeight="1" ht="18.75">
-      <c r="A1563" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1563" s="21"/>
-      <c r="C1563" s="10"/>
-      <c r="D1563" s="10"/>
-      <c r="E1563" s="10"/>
-      <c r="F1563" s="9"/>
-      <c r="G1563" s="9"/>
-      <c r="H1563" s="9"/>
-      <c r="I1563" s="7"/>
-      <c r="J1563" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1564" customHeight="1" ht="18.75">
-      <c r="A1564" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1564" s="21"/>
-      <c r="C1564" s="10"/>
-      <c r="D1564" s="10"/>
-      <c r="E1564" s="10"/>
-      <c r="F1564" s="9"/>
-      <c r="G1564" s="9"/>
-      <c r="H1564" s="9"/>
-      <c r="I1564" s="7"/>
-      <c r="J1564" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1565" customHeight="1" ht="18.75">
-      <c r="A1565" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1565" s="21"/>
-      <c r="C1565" s="10"/>
-      <c r="D1565" s="10"/>
-      <c r="E1565" s="10"/>
-      <c r="F1565" s="9"/>
-      <c r="G1565" s="9"/>
-      <c r="H1565" s="9"/>
-      <c r="I1565" s="7"/>
-      <c r="J1565" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1566" customHeight="1" ht="18.75">
-      <c r="A1566" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1566" s="21"/>
-      <c r="C1566" s="10"/>
-      <c r="D1566" s="10"/>
-      <c r="E1566" s="10"/>
-      <c r="F1566" s="9"/>
-      <c r="G1566" s="9"/>
-      <c r="H1566" s="9"/>
-      <c r="I1566" s="7"/>
-      <c r="J1566" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1567" customHeight="1" ht="18.75">
-      <c r="A1567" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1567" s="21"/>
-      <c r="C1567" s="10"/>
-      <c r="D1567" s="10"/>
-      <c r="E1567" s="10"/>
-      <c r="F1567" s="9"/>
-      <c r="G1567" s="9"/>
-      <c r="H1567" s="9"/>
-      <c r="I1567" s="7"/>
-      <c r="J1567" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1568" customHeight="1" ht="18.75">
-      <c r="A1568" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1568" s="21"/>
-      <c r="C1568" s="10"/>
-      <c r="D1568" s="10"/>
-      <c r="E1568" s="10"/>
-      <c r="F1568" s="9"/>
-      <c r="G1568" s="9"/>
-      <c r="H1568" s="9"/>
-      <c r="I1568" s="7"/>
-      <c r="J1568" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1569" customHeight="1" ht="18.75">
-      <c r="A1569" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1569" s="21"/>
-      <c r="C1569" s="10"/>
-      <c r="D1569" s="10"/>
-      <c r="E1569" s="10"/>
-      <c r="F1569" s="9"/>
-      <c r="G1569" s="9"/>
-      <c r="H1569" s="9"/>
-      <c r="I1569" s="7"/>
-      <c r="J1569" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1570" customHeight="1" ht="18.75">
-      <c r="A1570" s="6">
-        <f>IFERROR(_xlfn.IFS(AND(Tabla2[[#This Row], [Code]]&gt;0,Tabla2[[#This Row], [Lego]]&gt;0,Tabla2[[#This Row], [Cant.]]&gt;0,Tabla2[[#This Row], [TASK]]&gt;0,ISTEXT(Tabla2[[#This Row], [TASK]])=#REF!),"x",Tabla2[[#This Row], [Lego]]=0,"-",Tabla2[[#This Row], [TASK]]=0,""),"")</f>
-      </c>
-      <c r="B1570" s="21"/>
-      <c r="C1570" s="10"/>
-      <c r="D1570" s="10"/>
-      <c r="E1570" s="10"/>
-      <c r="F1570" s="9"/>
-      <c r="G1570" s="9"/>
-      <c r="H1570" s="9"/>
-      <c r="I1570" s="7"/>
-      <c r="J1570" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1571" customHeight="1" ht="18.75">
-      <c r="A1571" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1571" s="21"/>
-      <c r="C1571" s="23"/>
-      <c r="D1571" s="23"/>
-      <c r="E1571" s="23"/>
-      <c r="F1571" s="22"/>
-      <c r="G1571" s="22"/>
-      <c r="H1571" s="22"/>
-      <c r="I1571" s="23"/>
-      <c r="J1571" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
